--- a/output/2026-09-13_07_Croazia_Koprivnicko-krizevacka_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-13_07_Croazia_Koprivnicko-krizevacka_Impiantistica_aspirazione_industriale.xlsx
@@ -484,7 +484,6 @@
           <t>048 891227 / 091 1949660</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Confermata attività reale su fonti terze (tvrtke.hr, sito ufficiale): produzione canali ventilazione e isolamento impianti industriali, certificazioni dal 2013 per impianti industriali. Pertinente al settore.</t>
@@ -655,7 +654,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Filiale croata del produttore tedesco BERLINERLUFT. TECHNIK GmbH, confermata (Kompass, sito ufficiale). Forte pertinenza col settore. Candidato solido nonostante sede fuori contea.</t>
+          <t>Filiale croata del produttore tedesco BERLINERLUFT. TECHNIK GmbH, confermata (Kompass, sito ufficiale). Forte pertinenza col settore. Candidato solido nonostante sede fuori contea. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">

--- a/output/2026-09-13_07_Croazia_Koprivnicko-krizevacka_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-13_07_Croazia_Koprivnicko-krizevacka_Impiantistica_aspirazione_industriale.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
